--- a/WorkBot/refactor-experimental/data/orders/DUTCH VALLEY FOOD DIST/DUTCH VALLEY FOOD DIST_Bakery_20251005.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/DUTCH VALLEY FOOD DIST/DUTCH VALLEY FOOD DIST_Bakery_20251005.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,60 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>87.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>220252</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chocolate Block - Bronze Medal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>347.99</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1391.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>832400</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Register Tape - Thermal (3.125" x 230')</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>49.99</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>199.96</t>
         </is>
       </c>
     </row>
